--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/205.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/205.xlsx
@@ -426,13 +426,13 @@
         <v>-3.00996250601947</v>
       </c>
       <c r="E2">
-        <v>-18.19019836594427</v>
+        <v>-18.21686202090143</v>
       </c>
       <c r="F2">
-        <v>-6.241845032144209</v>
+        <v>-5.122374827571408</v>
       </c>
       <c r="G2">
-        <v>-10.55295102365569</v>
+        <v>-9.834258071444234</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.155054182743227</v>
       </c>
       <c r="E3">
-        <v>-19.64775565242309</v>
+        <v>-18.94842793989256</v>
       </c>
       <c r="F3">
-        <v>-5.566588504057449</v>
+        <v>-5.337238421244349</v>
       </c>
       <c r="G3">
-        <v>-10.01599377936806</v>
+        <v>-11.11587618715337</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.298739910714007</v>
       </c>
       <c r="E4">
-        <v>-18.95767508381623</v>
+        <v>-19.70805228383522</v>
       </c>
       <c r="F4">
-        <v>-5.757616654082237</v>
+        <v>-5.036271006254816</v>
       </c>
       <c r="G4">
-        <v>-10.2367608191999</v>
+        <v>-10.36054873800433</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.415595255202546</v>
       </c>
       <c r="E5">
-        <v>-19.88463559929032</v>
+        <v>-19.89669039709874</v>
       </c>
       <c r="F5">
-        <v>-4.933114413584193</v>
+        <v>-4.435635884730742</v>
       </c>
       <c r="G5">
-        <v>-10.71030125313725</v>
+        <v>-10.20373150635459</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.503221756531533</v>
       </c>
       <c r="E6">
-        <v>-22.31171652844132</v>
+        <v>-20.43745812072469</v>
       </c>
       <c r="F6">
-        <v>-5.876940493353297</v>
+        <v>-4.942720161987056</v>
       </c>
       <c r="G6">
-        <v>-10.69978364995899</v>
+        <v>-10.36862646912015</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.553564993023244</v>
       </c>
       <c r="E7">
-        <v>-21.00715373631165</v>
+        <v>-21.83137676197372</v>
       </c>
       <c r="F7">
-        <v>-4.998575319223022</v>
+        <v>-4.890098951091621</v>
       </c>
       <c r="G7">
-        <v>-9.524473772606932</v>
+        <v>-10.73264081443626</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.556797871665048</v>
       </c>
       <c r="E8">
-        <v>-20.34863663153824</v>
+        <v>-22.68378500985953</v>
       </c>
       <c r="F8">
-        <v>-5.006360316074532</v>
+        <v>-4.724415530122887</v>
       </c>
       <c r="G8">
-        <v>-8.840048277272468</v>
+        <v>-9.894261709343523</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.504864712721479</v>
       </c>
       <c r="E9">
-        <v>-24.11842821785954</v>
+        <v>-23.29274249509299</v>
       </c>
       <c r="F9">
-        <v>-5.758359699642548</v>
+        <v>-4.651866284618302</v>
       </c>
       <c r="G9">
-        <v>-8.448231970517565</v>
+        <v>-9.78085566135025</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.38784034210439</v>
       </c>
       <c r="E10">
-        <v>-22.88093212578346</v>
+        <v>-24.48929665366572</v>
       </c>
       <c r="F10">
-        <v>-5.466905255906764</v>
+        <v>-4.600829740564422</v>
       </c>
       <c r="G10">
-        <v>-8.877156182222159</v>
+        <v>-9.988287823749904</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.201858546706968</v>
       </c>
       <c r="E11">
-        <v>-23.90187206233874</v>
+        <v>-23.81652844119018</v>
       </c>
       <c r="F11">
-        <v>-5.681922097549223</v>
+        <v>-4.573959987119815</v>
       </c>
       <c r="G11">
-        <v>-8.997507754756823</v>
+        <v>-9.472335990908951</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.947197544733474</v>
       </c>
       <c r="E12">
-        <v>-25.85003969433455</v>
+        <v>-24.7901412958913</v>
       </c>
       <c r="F12">
-        <v>-5.807676552968217</v>
+        <v>-4.639548461338674</v>
       </c>
       <c r="G12">
-        <v>-8.142152172138708</v>
+        <v>-9.059785737441592</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.626715472877723</v>
       </c>
       <c r="E13">
-        <v>-24.73544185835264</v>
+        <v>-25.8985351224827</v>
       </c>
       <c r="F13">
-        <v>-5.316628640262698</v>
+        <v>-4.098026466045775</v>
       </c>
       <c r="G13">
-        <v>-9.017410754538922</v>
+        <v>-8.752772365220661</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.249079167407372</v>
       </c>
       <c r="E14">
-        <v>-26.32145836700705</v>
+        <v>-26.3812342239083</v>
       </c>
       <c r="F14">
-        <v>-5.224486020579698</v>
+        <v>-4.318195752933648</v>
       </c>
       <c r="G14">
-        <v>-8.909814713967068</v>
+        <v>-8.404916792681741</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.818954361922696</v>
       </c>
       <c r="E15">
-        <v>-27.68568380418778</v>
+        <v>-27.63504187936</v>
       </c>
       <c r="F15">
-        <v>-5.641501910129621</v>
+        <v>-4.217728040852513</v>
       </c>
       <c r="G15">
-        <v>-9.49341092381195</v>
+        <v>-7.444285861914802</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.345879661665098</v>
       </c>
       <c r="E16">
-        <v>-26.3941041470381</v>
+        <v>-26.10574450765167</v>
       </c>
       <c r="F16">
-        <v>-5.332790088291316</v>
+        <v>-4.416154340151703</v>
       </c>
       <c r="G16">
-        <v>-8.114303863062359</v>
+        <v>-7.064175644186764</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.8369879187303926</v>
       </c>
       <c r="E17">
-        <v>-26.55319396740157</v>
+        <v>-28.89950503415176</v>
       </c>
       <c r="F17">
-        <v>-4.579795835472537</v>
+        <v>-3.826574609985391</v>
       </c>
       <c r="G17">
-        <v>-6.998749332694147</v>
+        <v>-7.927456672825893</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.3007478516657887</v>
       </c>
       <c r="E18">
-        <v>-29.14389771939771</v>
+        <v>-29.49747870567961</v>
       </c>
       <c r="F18">
-        <v>-4.959953517434897</v>
+        <v>-4.076395308056472</v>
       </c>
       <c r="G18">
-        <v>-5.794763509880923</v>
+        <v>-7.241399078540568</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2479589090878958</v>
       </c>
       <c r="E19">
-        <v>-28.37571455958056</v>
+        <v>-29.67826670925083</v>
       </c>
       <c r="F19">
-        <v>-4.255761701784649</v>
+        <v>-3.960553096979378</v>
       </c>
       <c r="G19">
-        <v>-7.481344108681404</v>
+        <v>-6.31624395377246</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7954004854319057</v>
       </c>
       <c r="E20">
-        <v>-30.00643616363869</v>
+        <v>-30.06440968788488</v>
       </c>
       <c r="F20">
-        <v>-4.609350327669618</v>
+        <v>-3.213470073946977</v>
       </c>
       <c r="G20">
-        <v>-7.061590108120593</v>
+        <v>-6.52042184990701</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.319967516826186</v>
       </c>
       <c r="E21">
-        <v>-31.64803516226324</v>
+        <v>-31.2554640147753</v>
       </c>
       <c r="F21">
-        <v>-4.969536899917885</v>
+        <v>-3.059273623752863</v>
       </c>
       <c r="G21">
-        <v>-7.56262462276159</v>
+        <v>-6.421492817556969</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.796251705482568</v>
       </c>
       <c r="E22">
-        <v>-29.43162110818606</v>
+        <v>-31.60464106008473</v>
       </c>
       <c r="F22">
-        <v>-4.274929295118027</v>
+        <v>-3.224836103080789</v>
       </c>
       <c r="G22">
-        <v>-6.018576251608891</v>
+        <v>-5.919809435990275</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.197431930463456</v>
       </c>
       <c r="E23">
-        <v>-30.05057067131744</v>
+        <v>-31.72725402231642</v>
       </c>
       <c r="F23">
-        <v>-3.724310169007584</v>
+        <v>-2.999651879936368</v>
       </c>
       <c r="G23">
-        <v>-5.686230584921457</v>
+        <v>-5.929168348229794</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.490927461324247</v>
       </c>
       <c r="E24">
-        <v>-31.03783913938868</v>
+        <v>-32.26398234712753</v>
       </c>
       <c r="F24">
-        <v>-4.088052094148667</v>
+        <v>-2.912559816308236</v>
       </c>
       <c r="G24">
-        <v>-6.036764388801648</v>
+        <v>-6.56725613765108</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.649472664458967</v>
       </c>
       <c r="E25">
-        <v>-31.7755932181113</v>
+        <v>-32.31722361603571</v>
       </c>
       <c r="F25">
-        <v>-3.869107134282132</v>
+        <v>-3.011920001171829</v>
       </c>
       <c r="G25">
-        <v>-7.079076409659024</v>
+        <v>-6.628521093400833</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.654190572854209</v>
       </c>
       <c r="E26">
-        <v>-29.58286081885723</v>
+        <v>-32.51904185289855</v>
       </c>
       <c r="F26">
-        <v>-3.909856183560645</v>
+        <v>-2.814222665187102</v>
       </c>
       <c r="G26">
-        <v>-6.749154062306335</v>
+        <v>-6.703620818959199</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.492505162173313</v>
       </c>
       <c r="E27">
-        <v>-31.66351122218445</v>
+        <v>-32.53026567572657</v>
       </c>
       <c r="F27">
-        <v>-3.514999122035608</v>
+        <v>-2.976354875100035</v>
       </c>
       <c r="G27">
-        <v>-7.011084425373472</v>
+        <v>-6.385315175903814</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.167797025517795</v>
       </c>
       <c r="E28">
-        <v>-31.11066832261704</v>
+        <v>-31.75149494367948</v>
       </c>
       <c r="F28">
-        <v>-3.346621021905567</v>
+        <v>-2.903865272048453</v>
       </c>
       <c r="G28">
-        <v>-7.121219654373945</v>
+        <v>-6.649453672845644</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.692186373498021</v>
       </c>
       <c r="E29">
-        <v>-30.0641243940224</v>
+        <v>-31.40534518324417</v>
       </c>
       <c r="F29">
-        <v>-3.926234663848797</v>
+        <v>-2.301151776710755</v>
       </c>
       <c r="G29">
-        <v>-7.563826350792346</v>
+        <v>-6.484965907181416</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.086213759096454</v>
       </c>
       <c r="E30">
-        <v>-30.33868124463345</v>
+        <v>-30.80161808548957</v>
       </c>
       <c r="F30">
-        <v>-4.162500786107869</v>
+        <v>-2.769254740726131</v>
       </c>
       <c r="G30">
-        <v>-5.831921073013703</v>
+        <v>-6.661643101521241</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3832313934640543</v>
       </c>
       <c r="E31">
-        <v>-30.51604345761786</v>
+        <v>-31.88966321412751</v>
       </c>
       <c r="F31">
-        <v>-3.524352218380617</v>
+        <v>-2.866776778322911</v>
       </c>
       <c r="G31">
-        <v>-6.815732443646618</v>
+        <v>-7.060087120445764</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.3840838229765527</v>
       </c>
       <c r="E32">
-        <v>-29.45545220265143</v>
+        <v>-30.31877860136973</v>
       </c>
       <c r="F32">
-        <v>-3.922456480124629</v>
+        <v>-2.855018931407574</v>
       </c>
       <c r="G32">
-        <v>-7.156559728005665</v>
+        <v>-7.256382607651309</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.176341202090796</v>
       </c>
       <c r="E33">
-        <v>-27.66424147976146</v>
+        <v>-29.73566964577206</v>
       </c>
       <c r="F33">
-        <v>-3.368112185803797</v>
+        <v>-2.957393545249954</v>
       </c>
       <c r="G33">
-        <v>-7.318058071047932</v>
+        <v>-6.686468882520235</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.952040475415223</v>
       </c>
       <c r="E34">
-        <v>-29.15556759691548</v>
+        <v>-30.08315757027664</v>
       </c>
       <c r="F34">
-        <v>-3.395856695225761</v>
+        <v>-2.915156748116013</v>
       </c>
       <c r="G34">
-        <v>-8.139980454264947</v>
+        <v>-7.473130645198473</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.67612182484957</v>
       </c>
       <c r="E35">
-        <v>-27.30082691217191</v>
+        <v>-29.32908513546738</v>
       </c>
       <c r="F35">
-        <v>-3.014304042557086</v>
+        <v>-2.748022027457574</v>
       </c>
       <c r="G35">
-        <v>-8.058819119824173</v>
+        <v>-7.226091115966979</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.312995653996389</v>
       </c>
       <c r="E36">
-        <v>-25.70469832105838</v>
+        <v>-29.63317895779346</v>
       </c>
       <c r="F36">
-        <v>-2.861203522436876</v>
+        <v>-2.663227026637405</v>
       </c>
       <c r="G36">
-        <v>-7.649807839538298</v>
+        <v>-7.916230612902225</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.838335718644556</v>
       </c>
       <c r="E37">
-        <v>-27.27794000453714</v>
+        <v>-28.94063716356343</v>
       </c>
       <c r="F37">
-        <v>-3.572864726958167</v>
+        <v>-2.94168604255807</v>
       </c>
       <c r="G37">
-        <v>-8.090871821735398</v>
+        <v>-7.299134992745458</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.235784557431659</v>
       </c>
       <c r="E38">
-        <v>-26.03068957944854</v>
+        <v>-27.570687735237</v>
       </c>
       <c r="F38">
-        <v>-3.467141023706269</v>
+        <v>-2.465360703702507</v>
       </c>
       <c r="G38">
-        <v>-7.860679658753254</v>
+        <v>-7.80178505360962</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.495644693414943</v>
       </c>
       <c r="E39">
-        <v>-26.09925067592467</v>
+        <v>-26.68100561779405</v>
       </c>
       <c r="F39">
-        <v>-3.239898307565892</v>
+        <v>-2.57400357368187</v>
       </c>
       <c r="G39">
-        <v>-7.770516950991204</v>
+        <v>-7.695000096694888</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.621914084706895</v>
       </c>
       <c r="E40">
-        <v>-24.41093141096298</v>
+        <v>-27.09847657961317</v>
       </c>
       <c r="F40">
-        <v>-3.805458696520629</v>
+        <v>-2.644931704179175</v>
       </c>
       <c r="G40">
-        <v>-7.642448496804498</v>
+        <v>-7.36944104836296</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.622834428330159</v>
       </c>
       <c r="E41">
-        <v>-25.71881357454028</v>
+        <v>-26.04177075534531</v>
       </c>
       <c r="F41">
-        <v>-2.496348271506431</v>
+        <v>-2.215380130722686</v>
       </c>
       <c r="G41">
-        <v>-7.835416885743076</v>
+        <v>-8.422614969134685</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.517201579169642</v>
       </c>
       <c r="E42">
-        <v>-24.8533135082983</v>
+        <v>-23.69239844016593</v>
       </c>
       <c r="F42">
-        <v>-3.137988407836483</v>
+        <v>-2.809917639794753</v>
       </c>
       <c r="G42">
-        <v>-8.355735328150327</v>
+        <v>-7.962651082453886</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.326538071067119</v>
       </c>
       <c r="E43">
-        <v>-23.35437049786337</v>
+        <v>-25.68980417004715</v>
       </c>
       <c r="F43">
-        <v>-3.464998037235227</v>
+        <v>-2.77147393699823</v>
       </c>
       <c r="G43">
-        <v>-7.462344887831527</v>
+        <v>-7.767021014901733</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.075702601591677</v>
       </c>
       <c r="E44">
-        <v>-22.43619522196417</v>
+        <v>-25.02521891010347</v>
       </c>
       <c r="F44">
-        <v>-2.863461651976907</v>
+        <v>-2.547500786996703</v>
       </c>
       <c r="G44">
-        <v>-9.330767132013095</v>
+        <v>-8.165332612004685</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.793272343061407</v>
       </c>
       <c r="E45">
-        <v>-22.36813225762888</v>
+        <v>-23.97325892659565</v>
       </c>
       <c r="F45">
-        <v>-3.134640146794367</v>
+        <v>-2.526326059446342</v>
       </c>
       <c r="G45">
-        <v>-9.704256258662593</v>
+        <v>-8.112065934277812</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.502492225058325</v>
       </c>
       <c r="E46">
-        <v>-20.1971727614037</v>
+        <v>-23.74256940369691</v>
       </c>
       <c r="F46">
-        <v>-3.778029795079132</v>
+        <v>-2.548829488310793</v>
       </c>
       <c r="G46">
-        <v>-9.799073593452858</v>
+        <v>-8.355506900508118</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.233056234598185</v>
       </c>
       <c r="E47">
-        <v>-21.73717997414017</v>
+        <v>-22.82258726666864</v>
       </c>
       <c r="F47">
-        <v>-2.417270662500384</v>
+        <v>-2.66104179342882</v>
       </c>
       <c r="G47">
-        <v>-9.618592582288411</v>
+        <v>-8.610309659029204</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.004561747818834</v>
       </c>
       <c r="E48">
-        <v>-19.42143157846774</v>
+        <v>-22.6596754142427</v>
       </c>
       <c r="F48">
-        <v>-3.414134621968532</v>
+        <v>-2.499308856604036</v>
       </c>
       <c r="G48">
-        <v>-8.365882150228195</v>
+        <v>-8.20323835842934</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.835348987268376</v>
       </c>
       <c r="E49">
-        <v>-21.01262413291291</v>
+        <v>-21.37625606725483</v>
       </c>
       <c r="F49">
-        <v>-3.28225853144285</v>
+        <v>-2.395817603502683</v>
       </c>
       <c r="G49">
-        <v>-8.937328657943951</v>
+        <v>-8.444040819864847</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.740263956282342</v>
       </c>
       <c r="E50">
-        <v>-19.20967560539507</v>
+        <v>-21.49475717508755</v>
       </c>
       <c r="F50">
-        <v>-3.506439601662481</v>
+        <v>-2.419799668181131</v>
       </c>
       <c r="G50">
-        <v>-7.926946848812846</v>
+        <v>-8.387715198059688</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.719811462282603</v>
       </c>
       <c r="E51">
-        <v>-18.5255590370563</v>
+        <v>-20.3036779415901</v>
       </c>
       <c r="F51">
-        <v>-2.719323238787585</v>
+        <v>-2.518544376064443</v>
       </c>
       <c r="G51">
-        <v>-8.489524405028895</v>
+        <v>-8.675613480336867</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.780075911958806</v>
       </c>
       <c r="E52">
-        <v>-17.75034315710524</v>
+        <v>-20.25594782554925</v>
       </c>
       <c r="F52">
-        <v>-2.874705911102508</v>
+        <v>-2.324950772193185</v>
       </c>
       <c r="G52">
-        <v>-10.7460816293257</v>
+        <v>-8.427911841997519</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.912933518871965</v>
       </c>
       <c r="E53">
-        <v>-17.79402934585724</v>
+        <v>-19.68967120783809</v>
       </c>
       <c r="F53">
-        <v>-3.552270684957169</v>
+        <v>-2.11072833489001</v>
       </c>
       <c r="G53">
-        <v>-9.265360683793714</v>
+        <v>-9.280340902358917</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.108063695423318</v>
       </c>
       <c r="E54">
-        <v>-17.5391351293875</v>
+        <v>-18.678879581534</v>
       </c>
       <c r="F54">
-        <v>-3.784723003693752</v>
+        <v>-2.542003740911726</v>
       </c>
       <c r="G54">
-        <v>-8.750637063347831</v>
+        <v>-9.724341338449351</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.355547962492234</v>
       </c>
       <c r="E55">
-        <v>-16.6943528317306</v>
+        <v>-18.58666626531581</v>
       </c>
       <c r="F55">
-        <v>-2.217037693895688</v>
+        <v>-2.402738613153073</v>
       </c>
       <c r="G55">
-        <v>-10.07636488782221</v>
+        <v>-8.888256441415335</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.633651771973939</v>
       </c>
       <c r="E56">
-        <v>-16.56177722668204</v>
+        <v>-18.94653956623137</v>
       </c>
       <c r="F56">
-        <v>-2.734541176344415</v>
+        <v>-2.309950695263292</v>
       </c>
       <c r="G56">
-        <v>-10.14196996877395</v>
+        <v>-9.300432603236754</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.93139836002371</v>
       </c>
       <c r="E57">
-        <v>-17.0096795338327</v>
+        <v>-17.52758752066794</v>
       </c>
       <c r="F57">
-        <v>-3.360498661004666</v>
+        <v>-2.149659946086782</v>
       </c>
       <c r="G57">
-        <v>-11.11047337683328</v>
+        <v>-9.698509151606418</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.231353962692779</v>
       </c>
       <c r="E58">
-        <v>-15.75700852535692</v>
+        <v>-17.53648597209301</v>
       </c>
       <c r="F58">
-        <v>-2.208080557169217</v>
+        <v>-2.400444035447318</v>
       </c>
       <c r="G58">
-        <v>-11.163432173825</v>
+        <v>-9.709318082792139</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.51798855230255</v>
       </c>
       <c r="E59">
-        <v>-15.15163759153754</v>
+        <v>-18.59927806542717</v>
       </c>
       <c r="F59">
-        <v>-2.930070674836015</v>
+        <v>-2.38314358223985</v>
       </c>
       <c r="G59">
-        <v>-9.492666051065614</v>
+        <v>-10.03803208102299</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.784150670132058</v>
       </c>
       <c r="E60">
-        <v>-15.8139133297373</v>
+        <v>-17.59601276292383</v>
       </c>
       <c r="F60">
-        <v>-2.533761485253871</v>
+        <v>-2.238158577564867</v>
       </c>
       <c r="G60">
-        <v>-9.799788671289342</v>
+        <v>-9.60033492363933</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.016358982581687</v>
       </c>
       <c r="E61">
-        <v>-15.61508162148252</v>
+        <v>-17.81853744718675</v>
       </c>
       <c r="F61">
-        <v>-2.302668517425281</v>
+        <v>-2.189835765122558</v>
       </c>
       <c r="G61">
-        <v>-10.61353400702436</v>
+        <v>-9.897701366158826</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.213117082026908</v>
       </c>
       <c r="E62">
-        <v>-14.29782098823534</v>
+        <v>-17.44602517531579</v>
       </c>
       <c r="F62">
-        <v>-3.207913385408998</v>
+        <v>-2.187556098030053</v>
       </c>
       <c r="G62">
-        <v>-11.8993002362942</v>
+        <v>-10.04585490013229</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.369643261278788</v>
       </c>
       <c r="E63">
-        <v>-15.6569881199495</v>
+        <v>-18.31156146934984</v>
       </c>
       <c r="F63">
-        <v>-2.865195424950966</v>
+        <v>-2.302426634143663</v>
       </c>
       <c r="G63">
-        <v>-11.66853203838822</v>
+        <v>-9.37767425175903</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.481551636006712</v>
       </c>
       <c r="E64">
-        <v>-14.39046450948426</v>
+        <v>-15.60156865504363</v>
       </c>
       <c r="F64">
-        <v>-2.561351089971511</v>
+        <v>-2.586956754759446</v>
       </c>
       <c r="G64">
-        <v>-10.20956799814033</v>
+        <v>-10.29946586225924</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.551365372350426</v>
       </c>
       <c r="E65">
-        <v>-16.13055328930163</v>
+        <v>-16.15560027903805</v>
       </c>
       <c r="F65">
-        <v>-2.884121135002727</v>
+        <v>-2.775994337915308</v>
       </c>
       <c r="G65">
-        <v>-11.09554943754224</v>
+        <v>-9.687481724415106</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.574201361225531</v>
       </c>
       <c r="E66">
-        <v>-12.94089092268096</v>
+        <v>-16.25403571854278</v>
       </c>
       <c r="F66">
-        <v>-3.010054517780724</v>
+        <v>-2.582573034463831</v>
       </c>
       <c r="G66">
-        <v>-10.36118105220233</v>
+        <v>-9.346627955691744</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.555326275091113</v>
       </c>
       <c r="E67">
-        <v>-14.40143700200484</v>
+        <v>-15.57974593880067</v>
       </c>
       <c r="F67">
-        <v>-3.241170679896592</v>
+        <v>-2.765513833535088</v>
       </c>
       <c r="G67">
-        <v>-10.1951505723168</v>
+        <v>-9.200662692319739</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.495864732992612</v>
       </c>
       <c r="E68">
-        <v>-14.04916248047416</v>
+        <v>-16.4329330842158</v>
       </c>
       <c r="F68">
-        <v>-3.884474177971466</v>
+        <v>-2.59618393925923</v>
       </c>
       <c r="G68">
-        <v>-10.44242183973605</v>
+        <v>-9.30812962161556</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.397587616165694</v>
       </c>
       <c r="E69">
-        <v>-14.13878550955996</v>
+        <v>-15.59002104632407</v>
       </c>
       <c r="F69">
-        <v>-2.875830834035509</v>
+        <v>-2.465228993285462</v>
       </c>
       <c r="G69">
-        <v>-11.43935290234109</v>
+        <v>-10.11686279140412</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.26702608296561</v>
       </c>
       <c r="E70">
-        <v>-14.16724244022416</v>
+        <v>-14.9711326175918</v>
       </c>
       <c r="F70">
-        <v>-2.891772764702386</v>
+        <v>-2.46196771082064</v>
       </c>
       <c r="G70">
-        <v>-11.2919641043872</v>
+        <v>-10.11883587654552</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.101878067214549</v>
       </c>
       <c r="E71">
-        <v>-15.0451097689811</v>
+        <v>-15.18637551565038</v>
       </c>
       <c r="F71">
-        <v>-3.674600669532988</v>
+        <v>-2.883810497226677</v>
       </c>
       <c r="G71">
-        <v>-9.517892408074861</v>
+        <v>-8.798709495123587</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.908018140042425</v>
       </c>
       <c r="E72">
-        <v>-14.94152998300365</v>
+        <v>-16.75477626041494</v>
       </c>
       <c r="F72">
-        <v>-4.115785834794394</v>
+        <v>-2.810813104957179</v>
       </c>
       <c r="G72">
-        <v>-9.430378136744228</v>
+        <v>-9.558244647653037</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.684699829161925</v>
       </c>
       <c r="E73">
-        <v>-14.94530220185204</v>
+        <v>-16.13279035546142</v>
       </c>
       <c r="F73">
-        <v>-3.70844279140696</v>
+        <v>-2.682927260210783</v>
       </c>
       <c r="G73">
-        <v>-10.4593453485328</v>
+        <v>-9.491616608129664</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.432479490153197</v>
       </c>
       <c r="E74">
-        <v>-13.53522596534365</v>
+        <v>-15.52995536708633</v>
       </c>
       <c r="F74">
-        <v>-3.776111296174248</v>
+        <v>-3.226511890336652</v>
       </c>
       <c r="G74">
-        <v>-9.354857971902373</v>
+        <v>-8.636105429871206</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.155228342044698</v>
       </c>
       <c r="E75">
-        <v>-15.4895523219899</v>
+        <v>-16.82167540693026</v>
       </c>
       <c r="F75">
-        <v>-3.56906914751854</v>
+        <v>-2.768559740475182</v>
       </c>
       <c r="G75">
-        <v>-9.072720038863524</v>
+        <v>-9.006727624083693</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.850200978635318</v>
       </c>
       <c r="E76">
-        <v>-13.79449015923079</v>
+        <v>-16.20948911972933</v>
       </c>
       <c r="F76">
-        <v>-3.959290665057511</v>
+        <v>-2.936453245674586</v>
       </c>
       <c r="G76">
-        <v>-9.074209784356198</v>
+        <v>-8.94791909312408</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.523801786162087</v>
       </c>
       <c r="E77">
-        <v>-16.23574974049981</v>
+        <v>-16.16805358255915</v>
       </c>
       <c r="F77">
-        <v>-4.507297120379524</v>
+        <v>-3.430024365489032</v>
       </c>
       <c r="G77">
-        <v>-9.363760028857472</v>
+        <v>-9.01850654511242</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.176804070611679</v>
       </c>
       <c r="E78">
-        <v>-16.32047748918333</v>
+        <v>-16.86092821962874</v>
       </c>
       <c r="F78">
-        <v>-4.330102705981488</v>
+        <v>-3.487253784246241</v>
       </c>
       <c r="G78">
-        <v>-8.874067443234019</v>
+        <v>-8.537474346619698</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.813636618372682</v>
       </c>
       <c r="E79">
-        <v>-15.85759499001529</v>
+        <v>-17.59257112267801</v>
       </c>
       <c r="F79">
-        <v>-3.792523739525915</v>
+        <v>-3.776506427425384</v>
       </c>
       <c r="G79">
-        <v>-8.405347163601846</v>
+        <v>-8.792535327692848</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.442538492971512</v>
       </c>
       <c r="E80">
-        <v>-16.06818714526799</v>
+        <v>-17.84458975815287</v>
       </c>
       <c r="F80">
-        <v>-4.641182001856994</v>
+        <v>-2.993167419907254</v>
       </c>
       <c r="G80">
-        <v>-8.652472767017361</v>
+        <v>-8.214133363799082</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.067297986747657</v>
       </c>
       <c r="E81">
-        <v>-17.03333175357476</v>
+        <v>-18.36029237814638</v>
       </c>
       <c r="F81">
-        <v>-4.175000021848711</v>
+        <v>-3.588038761042649</v>
       </c>
       <c r="G81">
-        <v>-7.685313440446981</v>
+        <v>-7.726751538962039</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.700180492768854</v>
       </c>
       <c r="E82">
-        <v>-17.97481508519145</v>
+        <v>-20.19591837410357</v>
       </c>
       <c r="F82">
-        <v>-4.511655989653056</v>
+        <v>-3.543528095388023</v>
       </c>
       <c r="G82">
-        <v>-6.950229977270589</v>
+        <v>-6.966994579881458</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.348181811859363</v>
       </c>
       <c r="E83">
-        <v>-18.4910158373258</v>
+        <v>-20.52241229310859</v>
       </c>
       <c r="F83">
-        <v>-4.879412183228104</v>
+        <v>-3.642884966782004</v>
       </c>
       <c r="G83">
-        <v>-7.072922105501518</v>
+        <v>-7.035271271083387</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.019124123363833</v>
       </c>
       <c r="E84">
-        <v>-19.79793796441347</v>
+        <v>-20.81247916719591</v>
       </c>
       <c r="F84">
-        <v>-4.108392655724408</v>
+        <v>-3.980486930160345</v>
       </c>
       <c r="G84">
-        <v>-7.764862539210128</v>
+        <v>-6.895592733690457</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.722865811201342</v>
       </c>
       <c r="E85">
-        <v>-20.44548710514029</v>
+        <v>-21.4348047077</v>
       </c>
       <c r="F85">
-        <v>-4.89502856550568</v>
+        <v>-3.697162084115636</v>
       </c>
       <c r="G85">
-        <v>-7.161025653938142</v>
+        <v>-6.735719868507973</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4630488670584564</v>
       </c>
       <c r="E86">
-        <v>-21.41449903024961</v>
+        <v>-22.43307057489887</v>
       </c>
       <c r="F86">
-        <v>-4.600547267280068</v>
+        <v>-3.78863703967198</v>
       </c>
       <c r="G86">
-        <v>-7.993763589431956</v>
+        <v>-6.316982205427718</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2478611436057462</v>
       </c>
       <c r="E87">
-        <v>-23.60253087348371</v>
+        <v>-23.09070915571478</v>
       </c>
       <c r="F87">
-        <v>-4.727625453808734</v>
+        <v>-4.290873710887111</v>
       </c>
       <c r="G87">
-        <v>-5.972784785709692</v>
+        <v>-6.273859039233171</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.08176699222088309</v>
       </c>
       <c r="E88">
-        <v>-22.53045087995982</v>
+        <v>-23.83056218213995</v>
       </c>
       <c r="F88">
-        <v>-5.3466925784125</v>
+        <v>-4.262806966545459</v>
       </c>
       <c r="G88">
-        <v>-7.502677264136468</v>
+        <v>-6.572913859977694</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.03289467841331968</v>
       </c>
       <c r="E89">
-        <v>-24.164156748389</v>
+        <v>-25.46260157213431</v>
       </c>
       <c r="F89">
-        <v>-5.484360613818556</v>
+        <v>-4.510712479181267</v>
       </c>
       <c r="G89">
-        <v>-6.710414058405784</v>
+        <v>-6.677007343368999</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.08997173333099606</v>
       </c>
       <c r="E90">
-        <v>-28.29309255131061</v>
+        <v>-26.38039192774287</v>
       </c>
       <c r="F90">
-        <v>-5.316104283696726</v>
+        <v>-4.611171907588374</v>
       </c>
       <c r="G90">
-        <v>-6.803182165507241</v>
+        <v>-7.350812608613481</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.08905903958145964</v>
       </c>
       <c r="E91">
-        <v>-27.17286582213717</v>
+        <v>-28.21335518098356</v>
       </c>
       <c r="F91">
-        <v>-6.049191211091427</v>
+        <v>-4.601172684669181</v>
       </c>
       <c r="G91">
-        <v>-6.066678478294501</v>
+        <v>-5.939616429951734</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.0278824207839862</v>
       </c>
       <c r="E92">
-        <v>-29.56445710049006</v>
+        <v>-29.72908977303891</v>
       </c>
       <c r="F92">
-        <v>-5.867991640300854</v>
+        <v>-4.484103661468541</v>
       </c>
       <c r="G92">
-        <v>-6.968606815559083</v>
+        <v>-6.362051972399356</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.09507061235345624</v>
       </c>
       <c r="E93">
-        <v>-30.40079832259666</v>
+        <v>-29.86429642148593</v>
       </c>
       <c r="F93">
-        <v>-5.54787651279561</v>
+        <v>-4.750565432294461</v>
       </c>
       <c r="G93">
-        <v>-7.230421309532345</v>
+        <v>-7.192359967467344</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2754777179725439</v>
       </c>
       <c r="E94">
-        <v>-32.42949127939687</v>
+        <v>-33.17374371832049</v>
       </c>
       <c r="F94">
-        <v>-6.213003350097237</v>
+        <v>-5.198912662120471</v>
       </c>
       <c r="G94">
-        <v>-7.926599241531222</v>
+        <v>-7.511516420726323</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.511943103675881</v>
       </c>
       <c r="E95">
-        <v>-34.96069767564325</v>
+        <v>-34.28801323993685</v>
       </c>
       <c r="F95">
-        <v>-6.108583497137345</v>
+        <v>-5.579011529997232</v>
       </c>
       <c r="G95">
-        <v>-7.977551847926145</v>
+        <v>-8.0081909468921</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8018979419341944</v>
       </c>
       <c r="E96">
-        <v>-37.05790644417951</v>
+        <v>-36.33345702209144</v>
       </c>
       <c r="F96">
-        <v>-6.332446474274301</v>
+        <v>-5.349451870231225</v>
       </c>
       <c r="G96">
-        <v>-8.932538298548625</v>
+        <v>-7.732472161653899</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.132764459329926</v>
       </c>
       <c r="E97">
-        <v>-37.43407545881167</v>
+        <v>-39.26771119044249</v>
       </c>
       <c r="F97">
-        <v>-7.273524031000915</v>
+        <v>-5.82341636198881</v>
       </c>
       <c r="G97">
-        <v>-9.755672341433014</v>
+        <v>-8.075934640262206</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.510502917869761</v>
       </c>
       <c r="E98">
-        <v>-40.27731409231956</v>
+        <v>-41.26403914350988</v>
       </c>
       <c r="F98">
-        <v>-6.738165917552248</v>
+        <v>-6.034080132929557</v>
       </c>
       <c r="G98">
-        <v>-9.082456353294521</v>
+        <v>-8.768576909625141</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.909641466529712</v>
       </c>
       <c r="E99">
-        <v>-42.72339196993275</v>
+        <v>-42.72421615220214</v>
       </c>
       <c r="F99">
-        <v>-7.59561315802703</v>
+        <v>-6.114871634091997</v>
       </c>
       <c r="G99">
-        <v>-8.681304308118875</v>
+        <v>-8.308013814201734</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.351976842257842</v>
       </c>
       <c r="E100">
-        <v>-45.09632819961104</v>
+        <v>-44.93875768227715</v>
       </c>
       <c r="F100">
-        <v>-7.175449886530169</v>
+        <v>-6.007524330730611</v>
       </c>
       <c r="G100">
-        <v>-10.30509047913046</v>
+        <v>-9.56463400054383</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.790976424038656</v>
       </c>
       <c r="E101">
-        <v>-49.79449092105982</v>
+        <v>-47.26705900789884</v>
       </c>
       <c r="F101">
-        <v>-7.813709041305695</v>
+        <v>-6.359873304797291</v>
       </c>
       <c r="G101">
-        <v>-8.613110380555428</v>
+        <v>-9.298889889015454</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.290032064666402</v>
       </c>
       <c r="E102">
-        <v>-50.00306111266809</v>
+        <v>-49.75307123354866</v>
       </c>
       <c r="F102">
-        <v>-7.598929112740437</v>
+        <v>-6.572407115149859</v>
       </c>
       <c r="G102">
-        <v>-11.20661492983925</v>
+        <v>-10.0527176610352</v>
       </c>
     </row>
   </sheetData>
